--- a/backend/prueba_reporte_usuario.xlsx
+++ b/backend/prueba_reporte_usuario.xlsx
@@ -190,6 +190,36 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="495300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -489,17 +519,17 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Mis Solicitudes de Adopción</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Generado el 21/08/2026 01:54 (UTC) · Adoptify</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Generado el 23/08/2026 01:12 (UTC) · Adoptify</t>
         </is>
       </c>
     </row>
@@ -556,10 +586,11 @@
   </sheetData>
   <autoFilter ref="A4:E5"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>